--- a/B88/ib_results_B88_ibbylayer.xlsx
+++ b/B88/ib_results_B88_ibbylayer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\1DSubsidenceModeling-MF6CSUB\multib\1DSubsidenceModeling-MF6CSUB\B88\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interainc-my.sharepoint.com/personal/jwhite_intera_com/Documents/1d_csub/clay_thicknesses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFFF270-BB00-46F0-81C1-5F453C1E37DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_085D3E1F125E820F62355476582F76BDABD9812D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF37E9CE-0F94-45B4-8089-7E0D0E764DCB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
+    <t>Layer</t>
+  </si>
+  <si>
     <t>Aquifer Unit</t>
   </si>
   <si>
@@ -47,9 +50,6 @@
   </si>
   <si>
     <t>Lower</t>
-  </si>
-  <si>
-    <t>Layer</t>
   </si>
 </sst>
 </file>
@@ -68,7 +68,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,11 +108,9 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -421,35 +418,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -457,7 +447,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -556,7 +546,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2">
         <v>6</v>
@@ -598,7 +588,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2">
         <v>8</v>
